--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.00924040794686</v>
+        <v>6.989001566291364</v>
       </c>
       <c r="D2" t="n">
-        <v>43.21993355914001</v>
+        <v>7.023239203360252</v>
       </c>
       <c r="E2" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F2" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.36118416890106</v>
+        <v>6.721192427446423</v>
       </c>
       <c r="D3" t="n">
-        <v>41.47036817587755</v>
+        <v>6.738934828580102</v>
       </c>
       <c r="E3" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F3" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.30667404343136</v>
+        <v>7.037334532057596</v>
       </c>
       <c r="D4" t="n">
-        <v>43.28050403267325</v>
+        <v>7.033081905309404</v>
       </c>
       <c r="E4" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F4" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.90913792439576</v>
+        <v>7.622734912714311</v>
       </c>
       <c r="D5" t="n">
-        <v>46.8221894263186</v>
+        <v>7.608605781776773</v>
       </c>
       <c r="E5" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F5" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.83424696774835</v>
+        <v>5.660565132259107</v>
       </c>
       <c r="D6" t="n">
-        <v>35.09625380294237</v>
+        <v>5.703141242978136</v>
       </c>
       <c r="E6" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F6" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.43944386416819</v>
+        <v>4.133909627927331</v>
       </c>
       <c r="D7" t="n">
-        <v>25.66122834450303</v>
+        <v>4.169949605981742</v>
       </c>
       <c r="E7" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F7" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.3824996977489</v>
+        <v>8.512156200884196</v>
       </c>
       <c r="D8" t="n">
-        <v>52.22076571379765</v>
+        <v>8.485874428492117</v>
       </c>
       <c r="E8" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F8" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.51978735280782</v>
+        <v>8.37196544483127</v>
       </c>
       <c r="D9" t="n">
-        <v>51.31625734256193</v>
+        <v>8.338891818166314</v>
       </c>
       <c r="E9" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F9" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.50072035198194</v>
+        <v>7.231367057197065</v>
       </c>
       <c r="D10" t="n">
-        <v>44.75232913268374</v>
+        <v>7.272253484061108</v>
       </c>
       <c r="E10" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F10" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.97389798208159</v>
+        <v>6.495758422088258</v>
       </c>
       <c r="D11" t="n">
-        <v>40.17172668484295</v>
+        <v>6.527905586286979</v>
       </c>
       <c r="E11" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F11" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.18082926916628</v>
+        <v>3.116884756239521</v>
       </c>
       <c r="D12" t="n">
-        <v>19.18727734560786</v>
+        <v>3.117932568661278</v>
       </c>
       <c r="E12" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F12" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.16147851571121</v>
+        <v>3.926240258803071</v>
       </c>
       <c r="D13" t="n">
-        <v>23.98336228965383</v>
+        <v>3.897296372068747</v>
       </c>
       <c r="E13" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F13" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>28.97852033383025</v>
+        <v>4.709009554247416</v>
       </c>
       <c r="D14" t="n">
-        <v>28.71782987007769</v>
+        <v>4.666647353887625</v>
       </c>
       <c r="E14" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F14" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.93107978200643</v>
+        <v>6.813800464576045</v>
       </c>
       <c r="D15" t="n">
-        <v>41.99235759590147</v>
+        <v>6.82375810933399</v>
       </c>
       <c r="E15" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F15" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>38.79077053343228</v>
+        <v>6.303500211682746</v>
       </c>
       <c r="D16" t="n">
-        <v>38.54079293785986</v>
+        <v>6.262878852402228</v>
       </c>
       <c r="E16" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F16" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.8236927214916</v>
+        <v>5.821350067242385</v>
       </c>
       <c r="D17" t="n">
-        <v>35.72932456717896</v>
+        <v>5.806015242166581</v>
       </c>
       <c r="E17" t="n">
-        <v>9.335166831489671</v>
+        <v>1.516964610117072</v>
       </c>
       <c r="F17" t="n">
-        <v>9.328698871886612</v>
+        <v>1.515913566681574</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
